--- a/data.xlsx
+++ b/data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Artur\Проект\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C088B0-E23B-41D1-981E-179F794CDCEC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B552D4-213F-4E6D-8B96-BC72FF227655}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Объекты" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,19 +26,67 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Какие то данные</t>
+  </si>
+  <si>
+    <t>Ташкент</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>69.2401</t>
+  </si>
+  <si>
+    <t>41.2995</t>
+  </si>
+  <si>
+    <t>./src/svg/flag-svgrepo-com.svg</t>
+  </si>
+  <si>
+    <t>iconPath</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Titile</t>
+  </si>
+  <si>
+    <t>Самарканд</t>
+  </si>
+  <si>
+    <t>66.9597</t>
+  </si>
+  <si>
+    <t>39.6542</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -63,8 +112,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -356,4 +409,73 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CBB82D-396E-44F6-96C0-B3BCEEC60280}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Artur\Проект\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B552D4-213F-4E6D-8B96-BC72FF227655}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1FB68D-4DE3-4FBB-9473-A00D831D7630}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Какие то данные</t>
   </si>
@@ -65,6 +65,21 @@
   </si>
   <si>
     <t>39.6542</t>
+  </si>
+  <si>
+    <t>Ташкент2</t>
+  </si>
+  <si>
+    <t>Самарканд2</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Столица Узбекистана</t>
+  </si>
+  <si>
+    <t>Просто известный город</t>
   </si>
 </sst>
 </file>
@@ -413,15 +428,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CBB82D-396E-44F6-96C0-B3BCEEC60280}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -429,50 +445,59 @@
         <v>9</v>
       </c>
       <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="2"/>
       <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Artur\Проект\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1FB68D-4DE3-4FBB-9473-A00D831D7630}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7DF938-7332-4435-9313-31603E8856E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Объекты" sheetId="2" r:id="rId2"/>
+    <sheet name="Описание" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>Какие то данные</t>
   </si>
@@ -55,9 +56,6 @@
     <t>Group</t>
   </si>
   <si>
-    <t>Titile</t>
-  </si>
-  <si>
     <t>Самарканд</t>
   </si>
   <si>
@@ -67,12 +65,6 @@
     <t>39.6542</t>
   </si>
   <si>
-    <t>Ташкент2</t>
-  </si>
-  <si>
-    <t>Самарканд2</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -80,6 +72,45 @@
   </si>
   <si>
     <t>Просто известный город</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Общие сведения о государстве</t>
+  </si>
+  <si>
+    <t>Численность</t>
+  </si>
+  <si>
+    <t>15 млн.</t>
+  </si>
+  <si>
+    <t>Форма правления</t>
+  </si>
+  <si>
+    <t>Президенсткая</t>
+  </si>
+  <si>
+    <t>Экономика</t>
+  </si>
+  <si>
+    <t>ВВП</t>
+  </si>
+  <si>
+    <t>Внешняя политика</t>
+  </si>
+  <si>
+    <t>Поддерживает дружеские отношения со многими странами</t>
   </si>
 </sst>
 </file>
@@ -127,12 +158,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -428,79 +460,169 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CBB82D-396E-44F6-96C0-B3BCEEC60280}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
         <v>8</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>15</v>
       </c>
       <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2"/>
       <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E489711-A65C-4DB4-867D-2B209A811496}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Artur\Проект\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7DF938-7332-4435-9313-31603E8856E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE51680C-8E33-42EC-B66A-0BAF351E4872}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
   <si>
     <t>Какие то данные</t>
   </si>
@@ -111,6 +111,18 @@
   </si>
   <si>
     <t>Поддерживает дружеские отношения со многими странами</t>
+  </si>
+  <si>
+    <t>Изображения</t>
+  </si>
+  <si>
+    <t>img</t>
+  </si>
+  <si>
+    <t>.\src\img\Ташкент\1.jpg</t>
+  </si>
+  <si>
+    <t>.\src\img\Ташкент\2.jpg</t>
   </si>
 </sst>
 </file>
@@ -548,7 +560,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E489711-A65C-4DB4-867D-2B209A811496}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
@@ -618,8 +630,92 @@
       <c r="B5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Artur\Проект\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE51680C-8E33-42EC-B66A-0BAF351E4872}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8028CFB-D7FE-4953-8853-98663EF9741C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28365" yWindow="3285" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
   <si>
     <t>Какие то данные</t>
   </si>
@@ -123,6 +123,57 @@
   </si>
   <si>
     <t>.\src\img\Ташкент\2.jpg</t>
+  </si>
+  <si>
+    <t>radius</t>
+  </si>
+  <si>
+    <t>bColor</t>
+  </si>
+  <si>
+    <t>fColor</t>
+  </si>
+  <si>
+    <t>69.6698</t>
+  </si>
+  <si>
+    <t>39.6547</t>
+  </si>
+  <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>#FF6666</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>y1</t>
+  </si>
+  <si>
+    <t>Регистан</t>
+  </si>
+  <si>
+    <t>Площадь Регистан</t>
+  </si>
+  <si>
+    <t>64.38</t>
+  </si>
+  <si>
+    <t>39.75</t>
+  </si>
+  <si>
+    <t>39.76</t>
+  </si>
+  <si>
+    <t>64.42</t>
+  </si>
+  <si>
+    <t>Бухара</t>
+  </si>
+  <si>
+    <t>Площадь Бухара</t>
   </si>
 </sst>
 </file>
@@ -472,7 +523,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CBB82D-396E-44F6-96C0-B3BCEEC60280}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="11" bestFit="1" customWidth="1"/>
@@ -481,7 +532,7 @@
     <col min="7" max="7" width="36.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -503,8 +554,23 @@
       <c r="G1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -527,7 +593,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -551,6 +617,71 @@
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="2">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Artur\Проект\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8028CFB-D7FE-4953-8853-98663EF9741C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E023F1A4-C761-4801-96CC-E4A95A905ADB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28365" yWindow="3285" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="51">
   <si>
     <t>Какие то данные</t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>Площадь Бухара</t>
+  </si>
+  <si>
+    <t>Ташкент2</t>
+  </si>
+  <si>
+    <t>Ташкент3</t>
   </si>
 </sst>
 </file>
@@ -523,7 +529,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CBB82D-396E-44F6-96C0-B3BCEEC60280}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="11" bestFit="1" customWidth="1"/>
@@ -681,6 +687,52 @@
       </c>
       <c r="L5" s="1" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Artur\Проект\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E023F1A4-C761-4801-96CC-E4A95A905ADB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F158FF25-70EB-4395-BF35-6150555D26FB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -716,8 +716,8 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>1</v>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="C7" t="s">
         <v>50</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sav\Desktop\Проект карты\git load\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Artur\Проект\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47256737-6BE6-4ECC-AD7D-EF68ADF06161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD438B55-EB33-4B0D-8155-169292EB8C77}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Объекты" sheetId="2" r:id="rId1"/>
@@ -31,10 +31,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
     <t>x</t>
   </si>
@@ -87,6 +84,27 @@
   </si>
   <si>
     <t>scale</t>
+  </si>
+  <si>
+    <t>Ташкент</t>
+  </si>
+  <si>
+    <t>Город контрастов</t>
+  </si>
+  <si>
+    <t>41.30</t>
+  </si>
+  <si>
+    <t>69.26</t>
+  </si>
+  <si>
+    <t>.\src\svg\flag-svgrepo-com.svg</t>
+  </si>
+  <si>
+    <t>Крым</t>
+  </si>
+  <si>
+    <t>Городок</t>
   </si>
 </sst>
 </file>
@@ -411,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CBB82D-396E-44F6-96C0-B3BCEEC60280}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="57.28515625" bestFit="1" customWidth="1"/>
@@ -461,6 +479,52 @@
       </c>
       <c r="M1" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
